--- a/out/案件管理表_TeamEnergy.xlsx
+++ b/out/案件管理表_TeamEnergy.xlsx
@@ -1490,29 +1490,97 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="n"/>
+      <c r="A7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>株式会社SAMOEDO'S</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>犬とのふれあいを提供する体験型ペットサービス7店舗（札幌・仙台・大阪・岡山・広島・福岡2）。社員16名＋アルバイト84名</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>NG業種7カテゴリ</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>555.4</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>185.1</v>
+      </c>
       <c r="G7" s="15">
         <f>IF(OR($E7="",$F7="",$AG7="",$AH7="",$F7&lt;=0),"",($E7-($AG7-$AH7))/$F7)</f>
         <v/>
       </c>
-      <c r="H7" s="24" t="n"/>
-      <c r="I7" s="25" t="n"/>
-      <c r="J7" s="25" t="n"/>
-      <c r="K7" s="25" t="n"/>
-      <c r="L7" s="25" t="n"/>
-      <c r="M7" s="25" t="n"/>
-      <c r="N7" s="25" t="n"/>
-      <c r="O7" s="25" t="n"/>
-      <c r="P7" s="25" t="n"/>
-      <c r="Q7" s="25" t="n"/>
-      <c r="R7" s="25" t="n"/>
-      <c r="S7" s="25" t="n"/>
-      <c r="T7" s="25" t="n"/>
+      <c r="H7" s="14" t="n">
+        <v>423.9</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>×〜△</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>×〜△</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>△〜◯</t>
+        </is>
+      </c>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>◯</t>
+        </is>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>×〜△</t>
+        </is>
+      </c>
+      <c r="Q7" s="16" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <t>×〜△</t>
+        </is>
+      </c>
+      <c r="S7" s="16" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="T7" s="16" t="inlineStr">
+        <is>
+          <t>×〜△</t>
+        </is>
+      </c>
       <c r="U7" s="17">
         <f>IF($AN7=0,"",IF($AP7&gt;0,"C：見送り（Must×）",IF($AO7&gt;=2,"C：見送り（×2件以上）",IF($AN7&lt;6,"B：追加情報を取得",IF(AND($AO7=0,$AM7/($AN7*2)&gt;=0.75),"A：進める","B：追加情報を取得")))))</f>
         <v/>
@@ -1521,18 +1589,56 @@
         <f>IF($AN7=0,"",$AM7/($AN7*2))</f>
         <v/>
       </c>
-      <c r="W7" s="23" t="n"/>
-      <c r="X7" s="20" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="20" t="n"/>
-      <c r="AB7" s="20" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="23" t="n"/>
-      <c r="AE7" s="23" t="n"/>
-      <c r="AF7" s="23" t="n"/>
-      <c r="AG7" s="24" t="n"/>
-      <c r="AH7" s="24" t="n"/>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>見送り</t>
+        </is>
+      </c>
+      <c r="X7" s="13" t="inlineStr">
+        <is>
+          <t>見送りの連絡。業種NGの解釈だけ代表に確認</t>
+        </is>
+      </c>
+      <c r="Y7" s="19" t="n">
+        <v>46298</v>
+      </c>
+      <c r="Z7" s="19" t="n">
+        <v>46295</v>
+      </c>
+      <c r="AA7" s="13" t="inlineStr">
+        <is>
+          <t>倍率3.0倍で価格は◯。ただし業種がNG❶（消費者嗜好・流行依存）に該当し、8-2も×。設立2024年7月で業歴2期</t>
+        </is>
+      </c>
+      <c r="AB7" s="13" t="inlineStr">
+        <is>
+          <t>業種がNG❶（消費者嗜好・流行依存型業態）に該当。ブーム依存で8-2も×</t>
+        </is>
+      </c>
+      <c r="AC7" s="19" t="n">
+        <v>46268</v>
+      </c>
+      <c r="AD7" s="12" t="inlineStr">
+        <is>
+          <t>株式会社Anyglo</t>
+        </is>
+      </c>
+      <c r="AE7" s="12" t="inlineStr">
+        <is>
+          <t>尾仲様・室伏様</t>
+        </is>
+      </c>
+      <c r="AF7" s="12" t="inlineStr">
+        <is>
+          <t>東京都品川区</t>
+        </is>
+      </c>
+      <c r="AG7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="14" t="n">
+        <v>6.6</v>
+      </c>
       <c r="AI7" s="17">
         <f>IF($H7="","",IF($H7&lt;300,"下限未満（対象外）",IF($H7&gt;3000,"上限超（対象外）","範囲内")))</f>
         <v/>
@@ -1541,8 +1647,16 @@
         <f>IF(OR($E7="",$F7="",$AG7="",$F7&lt;=0),"",($E7-$AG7)/$F7)</f>
         <v/>
       </c>
-      <c r="AK7" s="23" t="n"/>
-      <c r="AL7" s="20" t="n"/>
+      <c r="AK7" s="12" t="inlineStr">
+        <is>
+          <t>仲介会社資料管理／Anyglo</t>
+        </is>
+      </c>
+      <c r="AL7" s="13" t="inlineStr">
+        <is>
+          <t>NNシート8/17受領・企業概要書9/3。意向表明期限が9月で実質期限切れ間近。両資料に第三者公表を控える旨の記載あり</t>
+        </is>
+      </c>
       <c r="AM7" s="21">
         <f>COUNTIF($I7:$T7,"◯")*2+COUNTIF($I7:$T7,"△〜◯")*1.5+COUNTIF($I7:$T7,"△")*1+COUNTIF($I7:$T7,"×〜△")*0.5</f>
         <v/>

--- a/out/案件管理表_TeamEnergy.xlsx
+++ b/out/案件管理表_TeamEnergy.xlsx
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>NG業種7カテゴリ</t>
+          <t>その他</t>
         </is>
       </c>
       <c r="E7" s="14" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>△</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="W7" s="12" t="inlineStr">
         <is>
-          <t>見送り</t>
+          <t>追加情報待ち</t>
         </is>
       </c>
       <c r="X7" s="13" t="inlineStr">
         <is>
-          <t>見送りの連絡。業種NGの解釈だけ代表に確認</t>
+          <t>質問リスト12項目を送付し、意向表明期限の延長可否を確認</t>
         </is>
       </c>
       <c r="Y7" s="19" t="n">
@@ -1607,14 +1607,10 @@
       </c>
       <c r="AA7" s="13" t="inlineStr">
         <is>
-          <t>倍率3.0倍で価格は◯。ただし業種がNG❶（消費者嗜好・流行依存）に該当し、8-2も×。設立2024年7月で業歴2期</t>
-        </is>
-      </c>
-      <c r="AB7" s="13" t="inlineStr">
-        <is>
-          <t>業種がNG❶（消費者嗜好・流行依存型業態）に該当。ブーム依存で8-2も×</t>
-        </is>
-      </c>
+          <t>倍率3.0倍・非キャッシュ性資産0.9倍で価格と資産は◯。業種はチェーン展開かつ動物で通常の飲食と毛色が違うため△（代表判断）。残る論点は業歴2期・ブーム依存(8-2×)・本部長不在の運営体制</t>
+        </is>
+      </c>
+      <c r="AB7" s="20" t="n"/>
       <c r="AC7" s="19" t="n">
         <v>46268</v>
       </c>
